--- a/Översikt KÄVLINGE.xlsx
+++ b/Översikt KÄVLINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44573</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45373</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45230</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 22369-2024</t>
+          <t>A 1468-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45446</v>
+        <v>44573</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>5.6</v>
+        <v>1.8</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 1468-2022</t>
+          <t>A 22369-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44573</v>
+        <v>45446</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.8</v>
+        <v>5.6</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1079,7 +1079,7 @@
         <v>45287</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>

--- a/Översikt KÄVLINGE.xlsx
+++ b/Översikt KÄVLINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44573</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45373</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45230</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
         <v>44573</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>45446</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>45287</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>

--- a/Översikt KÄVLINGE.xlsx
+++ b/Översikt KÄVLINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44573</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45373</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45230</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
         <v>44573</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>45446</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>45287</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>

--- a/Översikt KÄVLINGE.xlsx
+++ b/Översikt KÄVLINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44573</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45373</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45230</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 1468-2022</t>
+          <t>A 22369-2024</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44573</v>
+        <v>45446</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.8</v>
+        <v>5.6</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 22369-2024</t>
+          <t>A 1468-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45446</v>
+        <v>44573</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.6</v>
+        <v>1.8</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1079,7 +1079,7 @@
         <v>45287</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>

--- a/Översikt KÄVLINGE.xlsx
+++ b/Översikt KÄVLINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44573</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45373</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45230</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 22369-2024</t>
+          <t>A 1468-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45446</v>
+        <v>44573</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>5.6</v>
+        <v>1.8</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 1468-2022</t>
+          <t>A 22369-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44573</v>
+        <v>45446</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.8</v>
+        <v>5.6</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1079,7 +1079,7 @@
         <v>45287</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>

--- a/Översikt KÄVLINGE.xlsx
+++ b/Översikt KÄVLINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44573</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45373</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45230</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
         <v>44573</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>45446</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>45287</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>

--- a/Översikt KÄVLINGE.xlsx
+++ b/Översikt KÄVLINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44573</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45373</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45230</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
         <v>44573</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>45446</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>45287</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>

--- a/Översikt KÄVLINGE.xlsx
+++ b/Översikt KÄVLINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44573</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45373</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45230</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 1468-2022</t>
+          <t>A 22369-2024</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44573</v>
+        <v>45446</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.8</v>
+        <v>5.6</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 22369-2024</t>
+          <t>A 1468-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45446</v>
+        <v>44573</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.6</v>
+        <v>1.8</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1079,7 +1079,7 @@
         <v>45287</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>

--- a/Översikt KÄVLINGE.xlsx
+++ b/Översikt KÄVLINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44573</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45373</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45230</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 22369-2024</t>
+          <t>A 1468-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45446</v>
+        <v>44573</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>5.6</v>
+        <v>1.8</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 1468-2022</t>
+          <t>A 22369-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44573</v>
+        <v>45446</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.8</v>
+        <v>5.6</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1079,7 +1079,7 @@
         <v>45287</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>

--- a/Översikt KÄVLINGE.xlsx
+++ b/Översikt KÄVLINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44573</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45373</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45230</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 1468-2022</t>
+          <t>A 22369-2024</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44573</v>
+        <v>45446</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.8</v>
+        <v>5.6</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 22369-2024</t>
+          <t>A 1468-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45446</v>
+        <v>44573</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.6</v>
+        <v>1.8</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1079,7 +1079,7 @@
         <v>45287</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>

--- a/Översikt KÄVLINGE.xlsx
+++ b/Översikt KÄVLINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44573</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45373</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45230</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
         <v>45446</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>44573</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>45287</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>

--- a/Översikt KÄVLINGE.xlsx
+++ b/Översikt KÄVLINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44573</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45373</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45230</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
         <v>45446</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>44573</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>45287</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>

--- a/Översikt KÄVLINGE.xlsx
+++ b/Översikt KÄVLINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44573</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45373</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45230</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 22369-2024</t>
+          <t>A 1468-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45446</v>
+        <v>44573</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>5.6</v>
+        <v>1.8</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 1468-2022</t>
+          <t>A 22369-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44573</v>
+        <v>45446</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.8</v>
+        <v>5.6</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1079,7 +1079,7 @@
         <v>45287</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>

--- a/Översikt KÄVLINGE.xlsx
+++ b/Översikt KÄVLINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44573</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45373</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45230</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 1468-2022</t>
+          <t>A 22369-2024</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44573</v>
+        <v>45446</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.8</v>
+        <v>5.6</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 22369-2024</t>
+          <t>A 1468-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45446</v>
+        <v>44573</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.6</v>
+        <v>1.8</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1079,7 +1079,7 @@
         <v>45287</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>

--- a/Översikt KÄVLINGE.xlsx
+++ b/Översikt KÄVLINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44573</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45373</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45230</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 22369-2024</t>
+          <t>A 1468-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45446</v>
+        <v>44573</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>5.6</v>
+        <v>1.8</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 1468-2022</t>
+          <t>A 65018-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44573</v>
+        <v>45287</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1062,7 +1062,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 65018-2023</t>
+          <t>A 22369-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1072,14 +1072,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45287</v>
+        <v>45446</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.1</v>
+        <v>5.6</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>

--- a/Översikt KÄVLINGE.xlsx
+++ b/Översikt KÄVLINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44573</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45373</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45230</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 1468-2022</t>
+          <t>A 22369-2024</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44573</v>
+        <v>45446</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.8</v>
+        <v>5.6</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 65018-2023</t>
+          <t>A 1468-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45287</v>
+        <v>44573</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1062,7 +1062,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 22369-2024</t>
+          <t>A 65018-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1072,14 +1072,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45446</v>
+        <v>45287</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>5.6</v>
+        <v>1.1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>

--- a/Översikt KÄVLINGE.xlsx
+++ b/Översikt KÄVLINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44573</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45373</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45230</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 22369-2024</t>
+          <t>A 1468-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45446</v>
+        <v>44573</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>5.6</v>
+        <v>1.8</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 1468-2022</t>
+          <t>A 22369-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44573</v>
+        <v>45446</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.8</v>
+        <v>5.6</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1079,7 +1079,7 @@
         <v>45287</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>

--- a/Översikt KÄVLINGE.xlsx
+++ b/Översikt KÄVLINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44573</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45373</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45230</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
         <v>44573</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>45446</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>45287</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>

--- a/Översikt KÄVLINGE.xlsx
+++ b/Översikt KÄVLINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44573</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45373</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45230</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
         <v>44573</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>45446</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>45287</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>

--- a/Översikt KÄVLINGE.xlsx
+++ b/Översikt KÄVLINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44573</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45373</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45230</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 1468-2022</t>
+          <t>A 22369-2024</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44573</v>
+        <v>45446</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.8</v>
+        <v>5.6</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 22369-2024</t>
+          <t>A 1468-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45446</v>
+        <v>44573</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.6</v>
+        <v>1.8</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1079,7 +1079,7 @@
         <v>45287</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>

--- a/Översikt KÄVLINGE.xlsx
+++ b/Översikt KÄVLINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44573</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45373</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45230</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 22369-2024</t>
+          <t>A 1468-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45446</v>
+        <v>44573</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>5.6</v>
+        <v>1.8</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 1468-2022</t>
+          <t>A 22369-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44573</v>
+        <v>45446</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.8</v>
+        <v>5.6</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1079,7 +1079,7 @@
         <v>45287</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>

--- a/Översikt KÄVLINGE.xlsx
+++ b/Översikt KÄVLINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44573</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45373</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45230</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 1468-2022</t>
+          <t>A 65018-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -926,14 +926,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44573</v>
+        <v>45287</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -1006,7 +1006,7 @@
         <v>45446</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1062,7 +1062,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 65018-2023</t>
+          <t>A 1468-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1072,14 +1072,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45287</v>
+        <v>44573</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>

--- a/Översikt KÄVLINGE.xlsx
+++ b/Översikt KÄVLINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44573</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45373</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45230</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 65018-2023</t>
+          <t>A 1468-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -926,14 +926,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45287</v>
+        <v>44573</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -1006,7 +1006,7 @@
         <v>45446</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1062,7 +1062,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 1468-2022</t>
+          <t>A 65018-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1072,14 +1072,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44573</v>
+        <v>45287</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>

--- a/Översikt KÄVLINGE.xlsx
+++ b/Översikt KÄVLINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44573</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45373</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45230</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 1468-2022</t>
+          <t>A 65018-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -926,14 +926,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44573</v>
+        <v>45287</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -1006,7 +1006,7 @@
         <v>45446</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1062,7 +1062,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 65018-2023</t>
+          <t>A 1468-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1072,14 +1072,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45287</v>
+        <v>44573</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>

--- a/Översikt KÄVLINGE.xlsx
+++ b/Översikt KÄVLINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44573</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45373</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45230</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
         <v>45287</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>45446</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>44573</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>

--- a/Översikt KÄVLINGE.xlsx
+++ b/Översikt KÄVLINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44573</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45373</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45230</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
         <v>45287</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>45446</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>44573</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>

--- a/Översikt KÄVLINGE.xlsx
+++ b/Översikt KÄVLINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44573</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45373</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45230</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
         <v>45287</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 22369-2024</t>
+          <t>A 1468-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45446</v>
+        <v>44573</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.6</v>
+        <v>1.8</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1062,7 +1062,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 1468-2022</t>
+          <t>A 22369-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44573</v>
+        <v>45446</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.8</v>
+        <v>5.6</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>

--- a/Översikt KÄVLINGE.xlsx
+++ b/Översikt KÄVLINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44573</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45373</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45230</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 65018-2023</t>
+          <t>A 22369-2024</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -926,14 +926,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45287</v>
+        <v>45446</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.1</v>
+        <v>5.6</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -1006,7 +1006,7 @@
         <v>44573</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1062,7 +1062,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 22369-2024</t>
+          <t>A 65018-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1072,14 +1072,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45446</v>
+        <v>45287</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>5.6</v>
+        <v>1.1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>

--- a/Översikt KÄVLINGE.xlsx
+++ b/Översikt KÄVLINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44573</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45373</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45230</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 22369-2024</t>
+          <t>A 1468-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45446</v>
+        <v>44573</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>5.6</v>
+        <v>1.8</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 1468-2022</t>
+          <t>A 22369-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44573</v>
+        <v>45446</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.8</v>
+        <v>5.6</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1079,7 +1079,7 @@
         <v>45287</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>

--- a/Översikt KÄVLINGE.xlsx
+++ b/Översikt KÄVLINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44573</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45373</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45230</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 1468-2022</t>
+          <t>A 22369-2024</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44573</v>
+        <v>45446</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.8</v>
+        <v>5.6</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 22369-2024</t>
+          <t>A 1468-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45446</v>
+        <v>44573</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.6</v>
+        <v>1.8</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1079,7 +1079,7 @@
         <v>45287</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>

--- a/Översikt KÄVLINGE.xlsx
+++ b/Översikt KÄVLINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44573</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45373</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45230</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 22369-2024</t>
+          <t>A 1468-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45446</v>
+        <v>44573</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>5.6</v>
+        <v>1.8</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 1468-2022</t>
+          <t>A 22369-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44573</v>
+        <v>45446</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.8</v>
+        <v>5.6</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1079,7 +1079,7 @@
         <v>45287</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>

--- a/Översikt KÄVLINGE.xlsx
+++ b/Översikt KÄVLINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44573</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45373</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45230</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
         <v>44573</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>45446</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>45287</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>

--- a/Översikt KÄVLINGE.xlsx
+++ b/Översikt KÄVLINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44573</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45373</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45230</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
         <v>44573</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>45446</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>45287</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>

--- a/Översikt KÄVLINGE.xlsx
+++ b/Översikt KÄVLINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44573</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45373</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45230</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 1468-2022</t>
+          <t>A 22369-2024</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44573</v>
+        <v>45446</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.8</v>
+        <v>5.6</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 22369-2024</t>
+          <t>A 1468-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45446</v>
+        <v>44573</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.6</v>
+        <v>1.8</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1079,7 +1079,7 @@
         <v>45287</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>

--- a/Översikt KÄVLINGE.xlsx
+++ b/Översikt KÄVLINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44573</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45373</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45230</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 22369-2024</t>
+          <t>A 1468-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45446</v>
+        <v>44573</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>5.6</v>
+        <v>1.8</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 1468-2022</t>
+          <t>A 22369-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44573</v>
+        <v>45446</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.8</v>
+        <v>5.6</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1079,7 +1079,7 @@
         <v>45287</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>

--- a/Översikt KÄVLINGE.xlsx
+++ b/Översikt KÄVLINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44573</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45373</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45230</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 1468-2022</t>
+          <t>A 22369-2024</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44573</v>
+        <v>45446</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.8</v>
+        <v>5.6</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 22369-2024</t>
+          <t>A 1468-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45446</v>
+        <v>44573</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.6</v>
+        <v>1.8</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1079,7 +1079,7 @@
         <v>45287</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>

--- a/Översikt KÄVLINGE.xlsx
+++ b/Översikt KÄVLINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44573</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45373</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45230</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 22369-2024</t>
+          <t>A 1468-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45446</v>
+        <v>44573</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>5.6</v>
+        <v>1.8</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 1468-2022</t>
+          <t>A 22369-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44573</v>
+        <v>45446</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.8</v>
+        <v>5.6</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1079,7 +1079,7 @@
         <v>45287</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>

--- a/Översikt KÄVLINGE.xlsx
+++ b/Översikt KÄVLINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44573</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45373</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45230</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
         <v>44573</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 22369-2024</t>
+          <t>A 65018-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45446</v>
+        <v>45287</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.6</v>
+        <v>1.1</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1062,7 +1062,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 65018-2023</t>
+          <t>A 22369-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1072,14 +1072,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45287</v>
+        <v>45446</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.1</v>
+        <v>5.6</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>

--- a/Översikt KÄVLINGE.xlsx
+++ b/Översikt KÄVLINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44573</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45373</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45230</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
         <v>44573</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>45287</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>45446</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>

--- a/Översikt KÄVLINGE.xlsx
+++ b/Översikt KÄVLINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44573</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45373</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45230</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
         <v>44573</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>45287</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>45446</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>

--- a/Översikt KÄVLINGE.xlsx
+++ b/Översikt KÄVLINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44573</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45373</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45230</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
         <v>44573</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>45287</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>45446</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>

--- a/Översikt KÄVLINGE.xlsx
+++ b/Översikt KÄVLINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44573</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45373</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45230</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 1468-2022</t>
+          <t>A 65018-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -926,14 +926,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44573</v>
+        <v>45287</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 65018-2023</t>
+          <t>A 22369-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45287</v>
+        <v>45446</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.1</v>
+        <v>5.6</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1062,7 +1062,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 22369-2024</t>
+          <t>A 1468-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45446</v>
+        <v>44573</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>5.6</v>
+        <v>1.8</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>

--- a/Översikt KÄVLINGE.xlsx
+++ b/Översikt KÄVLINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44573</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45373</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45230</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 65018-2023</t>
+          <t>A 1468-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -926,14 +926,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45287</v>
+        <v>44573</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -1006,7 +1006,7 @@
         <v>45446</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1062,7 +1062,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 1468-2022</t>
+          <t>A 65018-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1072,14 +1072,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44573</v>
+        <v>45287</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>

--- a/Översikt KÄVLINGE.xlsx
+++ b/Översikt KÄVLINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44573</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45373</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45230</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
         <v>44573</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>45446</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>45287</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
